--- a/cms/packets.xlsx
+++ b/cms/packets.xlsx
@@ -1,37 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\githubrepo\kolibri-reports\cms\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4B33D0-5609-4C59-B12A-BA8604C7286E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="7905" yWindow="1080" windowWidth="19725" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="packets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="packets" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Date published</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Date start</t>
+  </si>
+  <si>
+    <t>Date end</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>Volume (collected)</t>
+  </si>
+  <si>
+    <t>Total estimated engagement</t>
+  </si>
+  <si>
+    <t>Gibran Peduli NTT, #PRAYFORNTT, wapres gibran, #bantuanNTT, #GempaNTT</t>
+  </si>
+  <si>
+    <t>gibran-&amp;-ntt-20260824</t>
+  </si>
+  <si>
+    <t>kesejahteraan guru indonesia</t>
+  </si>
+  <si>
+    <t>kesejahteraan-guru-2026-08-22-20260824</t>
+  </si>
+  <si>
+    <t>#BersamaPadamkanKebakaran OR #SinergiAtasiAsap OR #TindakTegasPembakarHutan OR "Pencegahan Karhutla Meluas" OR #PenangananKarhutla OR "Kompak Atasi Karhutla</t>
+  </si>
+  <si>
+    <t>Hadir Hingga Pelosok</t>
+  </si>
+  <si>
+    <t>#LawanNarkoba</t>
+  </si>
+  <si>
+    <t>#BareskrimPolri OR Polda Metro Jaya</t>
+  </si>
+  <si>
+    <t>Tentara Nasional Indonesia</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,85 +128,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,104 +436,158 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" customWidth="1"/>
+    <col min="5" max="7" width="19.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date published</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Keywords</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Date start</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Date end</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Volume (collected)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Total estimated engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46252.297222222223</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46256.744444444441</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>28253</v>
+      </c>
+      <c r="G2">
+        <v>4160126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46253.987500000003</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46255.345833333333</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>433</v>
+      </c>
+      <c r="G3">
+        <v>217094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>46258</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Gibran Peduli NTT, #PRAYFORNTT, wapres gibran, #bantuanNTT, #GempaNTT</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>46252.29722222222</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>46256.74444444444</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>gibran-&amp;-ntt-20260824</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>28253</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4160126</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46258.377083333333</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46258.668749999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>46258</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>kesejahteraan guru indonesia</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>46253.9875</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>46255.34583333333</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>kesejahteraan-guru-2026-08-22-20260824</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>433</v>
-      </c>
-      <c r="G3" t="n">
-        <v>217094</v>
-      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>46258.558333333334</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46258.779166666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>46258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5">
+        <v>46258.631249999999</v>
+      </c>
+      <c r="D6" s="5">
+        <v>46258.705555555556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>46258</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <v>46258.631249999999</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46258.779166666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46258</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46258.558333333334</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46258.779166666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cms/packets.xlsx
+++ b/cms/packets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\githubrepo\kolibri-reports\cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4B33D0-5609-4C59-B12A-BA8604C7286E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD7F8AE-E51A-4970-A27B-D403255B86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7905" yWindow="1080" windowWidth="19725" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Date published</t>
   </si>
@@ -81,6 +81,21 @@
   </si>
   <si>
     <t>Tentara Nasional Indonesia</t>
+  </si>
+  <si>
+    <t>#AspirasiDamaiPati OR "Dialog Tanpa Kekerasan" OR #AktivisSoundHoreg OR "Waspada Provokasi" OR "Dibalik Provokasi Pati" OR Pati</t>
+  </si>
+  <si>
+    <t>hadir hingga pelosok</t>
+  </si>
+  <si>
+    <t>#DanantaraUntukIndonesia OR "Danantara Indonesia"</t>
+  </si>
+  <si>
+    <t>#GercepAtasiKarhutla OR #UsutKejahatanLingkungan OR "Lindungi Hutan Lahan Indonesia" OR "pencegahan karhutla meluas" OR "kompak atasi karhutla"</t>
+  </si>
+  <si>
+    <t>RUU Perampasan Aset</t>
   </si>
 </sst>
 </file>
@@ -128,13 +143,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -587,7 +608,76 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4">
+        <v>46259</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46258.81527777778</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46259.772222222222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46259</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46259.071527777778</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46259.402083333334</v>
+      </c>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>46259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46259.363888888889</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46259.620833333334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46259</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46259.071527777778</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46259.772222222222</v>
+      </c>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46259</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="5">
+        <v>46259.620833333334</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46259.620833333334</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cms/packets.xlsx
+++ b/cms/packets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\githubrepo\kolibri-reports\cms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD7F8AE-E51A-4970-A27B-D403255B86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAAC0AA-BC45-4639-BFC4-C1E2ABE3F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7905" yWindow="1080" windowWidth="19725" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Date published</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>RUU Perampasan Aset</t>
+  </si>
+  <si>
+    <t>danantara indonesia</t>
+  </si>
+  <si>
+    <t>#AwasPenumpangGelapRUU OR "RUU Perampasan Aset"</t>
   </si>
 </sst>
 </file>
@@ -458,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -679,6 +685,50 @@
         <v>46259.620833333334</v>
       </c>
     </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46260</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46260.1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46260.50277777778</v>
+      </c>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46261</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5">
+        <v>46259.879166666666</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46260.87222222222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
